--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_336_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_336_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4873</v>
+        <v>7.824</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9657</v>
+        <v>6.2016</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5216</v>
+        <v>1.6224</v>
       </c>
       <c r="G2" t="n">
         <v>5.1082</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5461</v>
+        <v>-0.2093</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8215</v>
+        <v>-0.5856</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2754</v>
+        <v>0.3763</v>
       </c>
       <c r="V2" t="n">
         <v>0.1418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4913</v>
+        <v>4.6765</v>
       </c>
       <c r="E3" t="n">
-        <v>8.3071</v>
+        <v>8.4251</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.8158</v>
+        <v>-3.7485</v>
       </c>
       <c r="G3" t="n">
         <v>3.0237</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0299</v>
+        <v>0.1553</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3655</v>
+        <v>-0.2475</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3356</v>
+        <v>0.4028</v>
       </c>
       <c r="V3" t="n">
         <v>1.4975</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0692</v>
+        <v>2.2379</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9142</v>
+        <v>3.1501</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.845</v>
+        <v>-0.9122</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9862</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2847</v>
+        <v>-0.116</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6642</v>
+        <v>-0.4283</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3796</v>
+        <v>0.3123</v>
       </c>
       <c r="V4" t="n">
         <v>0.7886</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6637</v>
+        <v>1.3942</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7757</v>
+        <v>1.5398</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1119</v>
+        <v>-0.1455</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3501</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7639</v>
+        <v>0.4944</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4955</v>
+        <v>0.2596</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5396</v>
+        <v>1.2818</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06660000000000001</v>
+        <v>1.4252</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6062</v>
+        <v>-0.1435</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1912</v>
+        <v>0.7399</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9832</v>
+        <v>-1.833</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2079</v>
+        <v>2.573</v>
       </c>
       <c r="J6" t="n">
-        <v>0.293</v>
+        <v>1.8664</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3935</v>
+        <v>-0.131</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1005</v>
+        <v>1.9974</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4842</v>
+        <v>-1.1265</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3767</v>
+        <v>-1.7021</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1074</v>
+        <v>0.5756</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2473</v>
+        <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6585</v>
+        <v>0.06</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1845</v>
+        <v>-0.3536</v>
       </c>
       <c r="U6" t="n">
-        <v>0.843</v>
+        <v>0.4136</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1444</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1467</v>
+        <v>1.0177</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1893</v>
+        <v>-0.4205</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0426</v>
+        <v>1.4381</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7399</v>
+        <v>-2.1912</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.833</v>
+        <v>-0.9832</v>
       </c>
       <c r="I7" t="n">
-        <v>2.573</v>
+        <v>-1.2079</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8664</v>
+        <v>0.293</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.131</v>
+        <v>0.3935</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9974</v>
+        <v>-0.1005</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1265</v>
+        <v>-2.4842</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7021</v>
+        <v>-1.3767</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5756</v>
+        <v>-1.1074</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>3.2473</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0751</v>
+        <v>0.1366</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5895</v>
+        <v>-0.5384</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5144</v>
+        <v>0.675</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>2.1444</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7208</v>
+        <v>-0.4349</v>
       </c>
       <c r="E8" t="n">
-        <v>0.324</v>
+        <v>0.4419</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0448</v>
+        <v>-0.8768</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6939</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4187</v>
+        <v>-0.1327</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8962</v>
+        <v>-0.7782</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4775</v>
+        <v>0.6456</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8932</v>
+        <v>-0.6909</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2116</v>
+        <v>2.4475</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1049</v>
+        <v>-3.1385</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5718</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4116</v>
+        <v>-0.2093</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4846</v>
+        <v>0.4509</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9912</v>
+        <v>-1.6399</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3133</v>
+        <v>-0.9357</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.3044</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5252</v>
+        <v>-1.3332</v>
       </c>
       <c r="H10" t="n">
-        <v>2.834</v>
+        <v>-0.1788</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3088</v>
+        <v>-1.1544</v>
       </c>
       <c r="J10" t="n">
-        <v>4.0388</v>
+        <v>-0.7863</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5576</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5188</v>
+        <v>-0.7863</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5136</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7236</v>
+        <v>-0.1788</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.79</v>
+        <v>-0.368</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3935</v>
+        <v>-0.3066</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0578</v>
+        <v>-0.1494</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3356</v>
+        <v>-0.1573</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6399</v>
+        <v>-1.6729</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9357</v>
+        <v>1.1545</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-2.8274</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3332</v>
+        <v>-1.6498</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1788</v>
+        <v>-0.4921</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1544</v>
+        <v>-1.1577</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7863</v>
+        <v>0.8739</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.8739</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-2.5236</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1788</v>
+        <v>-1.366</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.368</v>
+        <v>-1.1577</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,19 +1312,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3066</v>
+        <v>-0.5592</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1494</v>
+        <v>-0.2555</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1573</v>
+        <v>-0.3038</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8161</v>
+        <v>-1.6811</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4464</v>
+        <v>-0.2105</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3697</v>
+        <v>-1.4705</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8182</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0742</v>
+        <v>0.2093</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U12" t="n">
-        <v>0.597</v>
+        <v>0.4962</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8917</v>
+        <v>-1.8676</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0366</v>
+        <v>2.3697</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9282</v>
+        <v>-4.2372</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6498</v>
+        <v>0.5252</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4921</v>
+        <v>2.834</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1577</v>
+        <v>-2.3088</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8739</v>
+        <v>4.0388</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8739</v>
+        <v>4.5576</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0.5188</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5236</v>
+        <v>-3.5136</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.366</v>
+        <v>-1.7236</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1577</v>
+        <v>-1.79</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.778</v>
+        <v>0.5171</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3734</v>
+        <v>0.1142</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4046</v>
+        <v>0.4028</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5361</v>
+        <v>-1.7501</v>
       </c>
       <c r="W13" t="n">
         <v>0.5361</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.4449</v>
+        <v>10.4448</v>
       </c>
       <c r="E14" t="n">
-        <v>25.5888</v>
+        <v>25.5887</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.1436</v>
+        <v>-15.1437</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1973999999999991</v>
+        <v>-0.197399999999999</v>
       </c>
       <c r="H14" t="n">
         <v>1.6267</v>
@@ -1546,7 +1546,7 @@
         <v>18.5562</v>
       </c>
       <c r="S14" t="n">
-        <v>0.03939999999999988</v>
+        <v>0.03959999999999997</v>
       </c>
       <c r="T14" t="n">
         <v>-3.9099</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1647</v>
+        <v>1.9845</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0429</v>
+        <v>5.6275</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.8783</v>
+        <v>-3.643</v>
       </c>
       <c r="G15" t="n">
         <v>1.2642</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9184</v>
+        <v>0.7382</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5454</v>
+        <v>0.13</v>
       </c>
       <c r="U15" t="n">
-        <v>0.373</v>
+        <v>0.6082</v>
       </c>
       <c r="V15" t="n">
         <v>0.6778999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0239</v>
+        <v>1.081</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1125</v>
+        <v>2.3484</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0886</v>
+        <v>-1.2674</v>
       </c>
       <c r="G16" t="n">
         <v>3.0965</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.275</v>
+        <v>0.3321</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7389</v>
+        <v>-0.503</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0139</v>
+        <v>0.8351</v>
       </c>
       <c r="V16" t="n">
         <v>4.147</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3648</v>
+        <v>-0.2976</v>
       </c>
       <c r="E17" t="n">
         <v>0.2261</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5909</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>0.2116</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2609</v>
+        <v>0.3282</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.857</v>
+        <v>-0.3646</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1326</v>
+        <v>1.3897</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7245</v>
+        <v>-1.7543</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7301</v>
+        <v>0.9613</v>
       </c>
       <c r="H18" t="n">
-        <v>0.006</v>
+        <v>0.2051</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7361</v>
+        <v>0.7562</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0168</v>
+        <v>4.2251</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0168</v>
+        <v>2.7798</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.4453</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7469</v>
+        <v>-3.2638</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0108</v>
+        <v>-2.5746</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7361</v>
+        <v>-0.6891</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.127</v>
+        <v>-0.0786</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1494</v>
+        <v>-0.4283</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.3497</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0266</v>
+        <v>-0.7055</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1538</v>
+        <v>-0.0146</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1804</v>
+        <v>-0.6909</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9613</v>
+        <v>-0.7301</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2051</v>
+        <v>0.006</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7562</v>
+        <v>-0.7361</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2251</v>
+        <v>0.0168</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7798</v>
+        <v>0.0168</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4453</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2638</v>
+        <v>-0.7469</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.5746</v>
+        <v>-0.0108</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6891</v>
+        <v>-0.7361</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7407</v>
+        <v>0.0246</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6642</v>
+        <v>-0.0314</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0764</v>
+        <v>0.056</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0889</v>
+        <v>-1.0374</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0223</v>
+        <v>1.8717</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1112</v>
+        <v>-2.9091</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.4695</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4046</v>
+        <v>-2.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0673</v>
+        <v>1.5928</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3596</v>
+        <v>2.5005</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1091</v>
+        <v>-0.5175</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>3.018</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0223</v>
+        <v>-2.97</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7045</v>
+        <v>-1.5448</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3178</v>
+        <v>-1.4252</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3154</v>
+        <v>0.1847</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2987</v>
+        <v>-0.6289</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0167</v>
+        <v>0.8136</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1107</v>
+        <v>-2.1444</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9615</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2019</v>
+        <v>-1.0669</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2566</v>
+        <v>2.4925</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4585</v>
+        <v>-3.5593</v>
       </c>
       <c r="G21" t="n">
         <v>2.0408</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.315</v>
+        <v>-0.1799</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5812</v>
+        <v>0.4804</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4471</v>
+        <v>-1.1333</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7537</v>
+        <v>1.0223</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2008</v>
+        <v>-2.1556</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4695</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0623</v>
+        <v>0.4046</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5928</v>
+        <v>-1.0673</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5005</v>
+        <v>0.3596</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5175</v>
+        <v>1.1091</v>
       </c>
       <c r="L22" t="n">
-        <v>3.018</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.97</v>
+        <v>-1.0223</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5448</v>
+        <v>-0.7045</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4252</v>
+        <v>-0.3178</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2249</v>
+        <v>-0.3598</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>-0.2987</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5219</v>
+        <v>-0.0611</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1444</v>
+        <v>-0.1107</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.9615</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1569</v>
+        <v>-1.9546</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5038</v>
+        <v>-0.2679</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6531</v>
+        <v>-1.6867</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9772</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0523</v>
+        <v>0.2546</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5149</v>
+        <v>-0.279</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5671</v>
+        <v>0.5335</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6588</v>
+        <v>-2.2549</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5266</v>
+        <v>-0.2907</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1322</v>
+        <v>-1.9642</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6449</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3361</v>
+        <v>0.0679</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1418</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8314</v>
+        <v>-3.9094</v>
       </c>
       <c r="E25" t="n">
         <v>0.7388</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.5702</v>
+        <v>-4.6481</v>
       </c>
       <c r="G25" t="n">
         <v>-1.8927</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1138</v>
+        <v>-0.1918</v>
       </c>
       <c r="T25" t="n">
         <v>-0.8215</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7077</v>
+        <v>0.6297</v>
       </c>
       <c r="V25" t="n">
         <v>-3.2166</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.4448</v>
+        <v>-9.6587</v>
       </c>
       <c r="E26" t="n">
-        <v>15.1437</v>
+        <v>15.1438</v>
       </c>
       <c r="F26" t="n">
-        <v>-25.5887</v>
+        <v>-24.8023</v>
       </c>
       <c r="G26" t="n">
         <v>0.1972</v>
@@ -2452,7 +2452,7 @@
         <v>-1.626599999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>1.823900000000001</v>
+        <v>1.8239</v>
       </c>
       <c r="J26" t="n">
         <v>29.829</v>
@@ -2473,7 +2473,7 @@
         <v>-11.6092</v>
       </c>
       <c r="P26" t="n">
-        <v>-9.278099999999998</v>
+        <v>-9.2781</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.5562</v>
@@ -2482,19 +2482,19 @@
         <v>9.278199999999998</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.03970000000000011</v>
+        <v>0.7468</v>
       </c>
       <c r="T26" t="n">
         <v>-3.9494</v>
       </c>
       <c r="U26" t="n">
-        <v>3.9098</v>
+        <v>4.696099999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-1.3247</v>
       </c>
       <c r="W26" t="n">
-        <v>7.8201</v>
+        <v>7.820099999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-9.1448</v>
